--- a/Results/Generator_GPT-4o_Analyser_GPT4.1.xlsx
+++ b/Results/Generator_GPT-4o_Analyser_GPT4.1.xlsx
@@ -27,7 +27,6 @@
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <family val="3"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
@@ -500,9 +499,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ANDY WARHOL</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Andy Warhol</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -527,7 +526,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -537,7 +536,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -547,54 +546,54 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CASPAR DAVID FRIEDRICH</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Camille Corot</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -604,29 +603,29 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EDGAR DEGAS</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Edgar Degas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -646,39 +645,39 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>HANS HOLBEIN THE YOUNGER</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Hans Holbein the Younger</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -688,7 +687,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -703,7 +702,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -713,12 +712,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -728,19 +727,19 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>JEAN-ANTOINE WATTEAU</t>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Jacob Jordaens</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -750,12 +749,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -765,17 +764,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -785,9 +784,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>JEAN-BAPTISTE CAMILLE COROT</t>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Michelangelo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -802,49 +801,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>JOSEPH-MALLORD WILLIAM TURNER</t>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Paul Gauguin</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -854,54 +853,54 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MICHELANGELO BUONARROTI</t>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Salvador Dali</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -916,12 +915,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -941,12 +940,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -956,81 +955,81 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PAUL GAUGUIN</t>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Vasily Vereshchagin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WILLIAM HOGARTH</t>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>William Turner</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1040,12 +1039,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1055,12 +1054,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1071,5 +1070,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>